--- a/artfynd/A 29946-2025 artfynd.xlsx
+++ b/artfynd/A 29946-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ50"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7349,6 +7349,566 @@
       <c r="AZ50" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129635628</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>137428670</v>
+      </c>
+      <c r="B51" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>694477</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6660175</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428670</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>137428671</v>
+      </c>
+      <c r="B52" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>694462</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6660191</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>3 m upp</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior # 3 m upp</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428671</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>137428673</v>
+      </c>
+      <c r="B53" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>694581</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6660262</v>
+      </c>
+      <c r="S53" t="n">
+        <v>5</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>2 m upp</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Viburnum opulus # 2 m upp</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428673</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>137428674</v>
+      </c>
+      <c r="B54" t="n">
+        <v>43487</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hygge syd om Västerbacken, Upl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>694515</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6660410</v>
+      </c>
+      <c r="S54" t="n">
+        <v>5</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>olvon</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Viburnum opulus</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>1 m upp</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Viburnum opulus # 1 m upp</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428674</t>
         </is>
       </c>
     </row>
@@ -7403,6 +7963,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
